--- a/samples/output/sample_errors_BOM展開.xlsx
+++ b/samples/output/sample_errors_BOM展開.xlsx
@@ -8,7 +8,8 @@
   <x:sheets>
     <x:sheet name="BOM展開" sheetId="1" r:id="rId2"/>
     <x:sheet name="部品集計" sheetId="2" r:id="rId3"/>
-    <x:sheet name="エラー" sheetId="3" r:id="rId4"/>
+    <x:sheet name="逆展開" sheetId="3" r:id="rId4"/>
+    <x:sheet name="エラー" sheetId="4" r:id="rId5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">BOM展開!$A$1:$G$8</x:definedName>
@@ -17,9 +18,12 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="1">部品集計!$A$1:$G$7</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">部品集計!$A$1:$G$7</x:definedName>
     <x:definedName name="_xlnm.Print_Titles" localSheetId="1">部品集計!1:1</x:definedName>
-    <x:definedName name="_xlnm.Print_Area" localSheetId="2">エラー!$A$1:$D$11</x:definedName>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">エラー!$A$1:$D$11</x:definedName>
-    <x:definedName name="_xlnm.Print_Titles" localSheetId="2">エラー!1:1</x:definedName>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="2">逆展開!$A$1:$J$20</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">逆展開!$A$1:$J$20</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles" localSheetId="2">逆展開!1:1</x:definedName>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="3">エラー!$A$1:$D$11</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">エラー!$A$1:$D$11</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles" localSheetId="3">エラー!1:1</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -112,6 +116,19 @@
   </x:si>
   <x:si>
     <x:t>使用箇所数</x:t>
+  </x:si>
+  <x:si>
+    <x:t>部品品番</x:t>
+  </x:si>
+  <x:si>
+    <x:t>部品品名</x:t>
+  </x:si>
+  <x:si>
+    <x:t>累計員数
+（この品番1個あたり）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>製品</x:t>
   </x:si>
   <x:si>
     <x:t>行番号</x:t>
@@ -243,7 +260,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -262,6 +279,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFCE4D6"/>
       </x:patternFill>
     </x:fill>
@@ -438,7 +460,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="16">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -481,14 +503,41 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="8" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="8" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="8" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -597,7 +646,71 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="2" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="4" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="6" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="8" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -605,7 +718,7 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1326,6 +1439,647 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
     <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
+  <x:dimension ref="A1:J20"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="13.510625" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="20.110625" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="11.310625" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="23.410625" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="20.110625" style="1" customWidth="1"/>
+    <x:col min="6" max="6" width="9.110625" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="27.810625" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="9.110625" style="2" customWidth="1"/>
+    <x:col min="9" max="9" width="13.510625" style="2" customWidth="1"/>
+    <x:col min="10" max="10" width="10.210625" style="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:10" ht="30" customHeight="1">
+      <x:c r="A1" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C1" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E1" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F1" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J1" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10">
+      <x:c r="A2" s="27" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B2" s="28" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C2" s="29">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="28" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="28" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="28"/>
+      <x:c r="G2" s="28">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="29" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I2" s="29" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J2" s="30"/>
+    </x:row>
+    <x:row r="3" spans="1:10">
+      <x:c r="A3" s="31" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="32" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E3" s="32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F3" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" s="33" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I3" s="33" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J3" s="35" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:10">
+      <x:c r="A4" s="36" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="37" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C4" s="38">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="37" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E4" s="37" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F4" s="37"/>
+      <x:c r="G4" s="37">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="38" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I4" s="38" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J4" s="39"/>
+    </x:row>
+    <x:row r="5" spans="1:10">
+      <x:c r="A5" s="23" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C5" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F5" s="12">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G5" s="12">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H5" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I5" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J5" s="24"/>
+    </x:row>
+    <x:row r="6" spans="1:10">
+      <x:c r="A6" s="31" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="32" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C6" s="33">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="40" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E6" s="32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F6" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H6" s="33" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I6" s="33" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J6" s="35" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:10">
+      <x:c r="A7" s="36" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B7" s="37" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C7" s="38">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" s="37"/>
+      <x:c r="G7" s="37">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="38" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I7" s="38" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J7" s="39"/>
+    </x:row>
+    <x:row r="8" spans="1:10">
+      <x:c r="A8" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C8" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="12">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="12">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I8" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J8" s="24"/>
+    </x:row>
+    <x:row r="9" spans="1:10">
+      <x:c r="A9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B9" s="32" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C9" s="33">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D9" s="40" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E9" s="32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F9" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="33" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I9" s="33" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J9" s="35" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:10">
+      <x:c r="A10" s="36" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B10" s="37" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="38">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="37" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E10" s="37" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F10" s="37"/>
+      <x:c r="G10" s="37">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="38" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I10" s="38" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J10" s="39"/>
+    </x:row>
+    <x:row r="11" spans="1:10">
+      <x:c r="A11" s="23" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C11" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="12">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G11" s="12">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H11" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J11" s="24"/>
+    </x:row>
+    <x:row r="12" spans="1:10">
+      <x:c r="A12" s="23" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C12" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E12" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F12" s="12">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="12">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H12" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I12" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J12" s="24"/>
+    </x:row>
+    <x:row r="13" spans="1:10">
+      <x:c r="A13" s="31" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B13" s="32" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C13" s="33">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D13" s="41" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E13" s="32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F13" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H13" s="33" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I13" s="33" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J13" s="35" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
+      <x:c r="A14" s="36" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B14" s="37" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C14" s="38">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="37" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E14" s="37" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F14" s="37"/>
+      <x:c r="G14" s="37">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="38" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I14" s="38" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J14" s="39"/>
+    </x:row>
+    <x:row r="15" spans="1:10">
+      <x:c r="A15" s="23" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C15" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F15" s="12">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G15" s="12">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H15" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J15" s="24"/>
+    </x:row>
+    <x:row r="16" spans="1:10">
+      <x:c r="A16" s="23" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C16" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="12">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G16" s="12">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J16" s="24"/>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="23" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E17" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F17" s="12">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="12">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J17" s="24"/>
+    </x:row>
+    <x:row r="18" spans="1:10">
+      <x:c r="A18" s="31" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B18" s="32" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C18" s="33">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D18" s="42" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E18" s="32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F18" s="32">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="32">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H18" s="33" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I18" s="33" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J18" s="35" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:10">
+      <x:c r="A19" s="36" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B19" s="37" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C19" s="38">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="37" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E19" s="37" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F19" s="37"/>
+      <x:c r="G19" s="37">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="38" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I19" s="38" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J19" s="39"/>
+    </x:row>
+    <x:row r="20" spans="1:10">
+      <x:c r="A20" s="31" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B20" s="32" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C20" s="33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D20" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E20" s="32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F20" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G20" s="32">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H20" s="33" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I20" s="33" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J20" s="35" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:autoFilter ref="A1:J20"/>
+  <x:printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="9" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader>&amp;L逆展開</x:oddHeader>
+    <x:oddFooter>&amp;C&amp;P / &amp;N</x:oddFooter>
+    <x:evenHeader>&amp;L逆展開</x:evenHeader>
+    <x:evenFooter>&amp;C&amp;P / &amp;N</x:evenFooter>
+    <x:firstHeader>&amp;L逆展開</x:firstHeader>
+    <x:firstFooter>&amp;C&amp;P / &amp;N</x:firstFooter>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+    <x:pageSetUpPr fitToPage="1"/>
+  </x:sheetPr>
   <x:dimension ref="A1:D11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1338,156 +2092,156 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="30" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D1" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="10">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B2" s="27" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C2" s="28" t="s">
-        <x:v>33</x:v>
+      <x:c r="B2" s="43" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C2" s="44" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D2" s="24" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="10">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B3" s="27" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C3" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="B3" s="43" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C3" s="44" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D3" s="24" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="10">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B4" s="27" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C4" s="28" t="s">
-        <x:v>37</x:v>
+      <x:c r="B4" s="43" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C4" s="44" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="24" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="10">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B5" s="27" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C5" s="28" t="s">
-        <x:v>40</x:v>
+      <x:c r="B5" s="43" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C5" s="44" t="s">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D5" s="24" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="10">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C6" s="28" t="s">
-        <x:v>42</x:v>
+      <x:c r="B6" s="43" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C6" s="44" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D6" s="24" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="10">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B7" s="27" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C7" s="28" t="s">
-        <x:v>45</x:v>
+      <x:c r="B7" s="43" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C7" s="44" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D7" s="24" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="10">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B8" s="27" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C8" s="28" t="s">
-        <x:v>48</x:v>
+      <x:c r="B8" s="43" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C8" s="44" t="s">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D8" s="24" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="10">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B9" s="27" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C9" s="28" t="s">
-        <x:v>51</x:v>
+      <x:c r="B9" s="43" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C9" s="44" t="s">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="24" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="10">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B10" s="27" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>54</x:v>
+      <x:c r="B10" s="43" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C10" s="44" t="s">
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D10" s="24" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="18">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B11" s="29" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C11" s="30" t="s">
-        <x:v>56</x:v>
+      <x:c r="B11" s="45" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C11" s="46" t="s">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D11" s="26" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
